--- a/sheets/조재수대금교본/검수/어디로 갈거나.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 갈거나.xlsx
@@ -3920,7 +3920,7 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-林∧</t>
+林</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3932,7 +3932,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∽</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -3946,7 +3946,7 @@
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-林∧</t>
+林</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3959,7 +3959,7 @@
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-林∧</t>
+林</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -3972,49 +3972,21 @@
     </row>
     <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B4" s="21"/>
       <c r="C4" s="23"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D4" s="21"/>
       <c r="E4" s="23"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N4" s="21"/>
       <c r="O4" s="23"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="90.2" customHeight="true">
@@ -4022,8 +3994,7 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="C5" s="24"/>
@@ -4036,23 +4007,16 @@
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∼
-‹</t>
+          <t xml:space="preserve">南∼</t>
         </is>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-Z</t>
-        </is>
-      </c>
+      <c r="H5" s="21"/>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -4066,8 +4030,7 @@
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="O5" s="24"/>
@@ -4102,11 +4065,7 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -4188,55 +4147,35 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="90.2" customHeight="true">
@@ -4250,7 +4189,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㅅ
+          <t xml:space="preserve">太
 –</t>
         </is>
       </c>
@@ -4277,7 +4216,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㅅ
+          <t xml:space="preserve">太
 –</t>
         </is>
       </c>
@@ -4291,7 +4230,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㅅ
+          <t xml:space="preserve">太
 –</t>
         </is>
       </c>
@@ -4306,11 +4245,7 @@
         </is>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -4319,11 +4254,7 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -4332,11 +4263,7 @@
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
@@ -4345,19 +4272,14 @@
         </is>
       </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="C11" s="24"/>
@@ -4370,16 +4292,11 @@
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼
-‹</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G11" s="24"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H11" s="21"/>
       <c r="I11" s="24"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
@@ -4408,7 +4325,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㄷ</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -4421,7 +4338,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㄷ</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4434,7 +4351,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㄷ</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -4447,7 +4364,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㄷ</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -4461,11 +4378,7 @@
     </row>
     <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="B13" s="21"/>
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
@@ -4473,11 +4386,7 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="F13" s="21"/>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
@@ -4486,11 +4395,7 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="J13" s="21"/>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4498,11 +4403,7 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N13" s="21"/>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
@@ -4513,55 +4414,26 @@
     </row>
     <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–∼
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/어디로 갈거나.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 갈거나.xlsx
@@ -3920,7 +3920,7 @@
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-林</t>
+林∧</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -3932,7 +3932,7 @@
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢∽</t>
         </is>
       </c>
       <c r="G3" s="22"/>
@@ -3946,7 +3946,7 @@
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-林</t>
+林∧</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3959,7 +3959,7 @@
       <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-林</t>
+林∧</t>
         </is>
       </c>
       <c r="O3" s="22"/>
@@ -3972,21 +3972,49 @@
     </row>
     <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
-      <c r="B4" s="21"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C4" s="23"/>
-      <c r="D4" s="21"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E4" s="23"/>
       <c r="F4" s="21"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="21"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I4" s="23"/>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="90.2" customHeight="true">
@@ -4011,7 +4039,12 @@
         </is>
       </c>
       <c r="G5" s="24"/>
-      <c r="H5" s="21"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+Z</t>
+        </is>
+      </c>
       <c r="I5" s="24"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
@@ -4065,7 +4098,11 @@
         </is>
       </c>
       <c r="G6" s="22"/>
-      <c r="H6" s="21"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
@@ -4189,7 +4226,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ㅅ
 –</t>
         </is>
       </c>
@@ -4216,7 +4253,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ㅅ
 –</t>
         </is>
       </c>
@@ -4230,7 +4267,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ㅅ
 –</t>
         </is>
       </c>
@@ -4245,7 +4282,11 @@
         </is>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -4254,7 +4295,11 @@
         </is>
       </c>
       <c r="G10" s="23"/>
-      <c r="H10" s="21"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="I10" s="23"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
@@ -4263,7 +4308,11 @@
         </is>
       </c>
       <c r="K10" s="23"/>
-      <c r="L10" s="21"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M10" s="23"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
@@ -4272,7 +4321,11 @@
         </is>
       </c>
       <c r="O10" s="23"/>
-      <c r="P10" s="21"/>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q10" s="23"/>
     </row>
     <row r="11" ht="90.2" customHeight="true">
@@ -4325,7 +4378,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㄷ</t>
         </is>
       </c>
       <c r="C12" s="22"/>
@@ -4338,7 +4391,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㄷ</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4351,7 +4404,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㄷ</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -4364,7 +4417,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">太ㄷ</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -4378,7 +4431,11 @@
     </row>
     <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
-      <c r="B13" s="21"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
@@ -4386,7 +4443,11 @@
         </is>
       </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="21"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
@@ -4395,7 +4456,11 @@
         </is>
       </c>
       <c r="I13" s="23"/>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
@@ -4403,7 +4468,11 @@
         </is>
       </c>
       <c r="M13" s="23"/>
-      <c r="N13" s="21"/>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O13" s="23"/>
       <c r="P13" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/어디로 갈거나.xlsx
+++ b/sheets/조재수대금교본/검수/어디로 갈거나.xlsx
@@ -3871,28 +3871,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4511,6 +4511,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>